--- a/meta-analysis data.xlsx
+++ b/meta-analysis data.xlsx
@@ -17,30 +17,30 @@
     <t>Study</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>Pain scale</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
     <t>Procedure step</t>
   </si>
   <si>
     <t>Arm</t>
   </si>
   <si>
+    <t>Total n</t>
+  </si>
+  <si>
     <t>Mean</t>
   </si>
   <si>
-    <t>Total n</t>
+    <t>Participants in paracervical block arm</t>
   </si>
   <si>
     <t>SD of mean</t>
   </si>
   <si>
-    <t>Participants in paracervical block arm</t>
-  </si>
-  <si>
     <t>Median</t>
   </si>
   <si>
@@ -56,21 +56,24 @@
     <t>Upper 95 CI of median</t>
   </si>
   <si>
+    <t>Q1</t>
+  </si>
+  <si>
     <t>Paracervical block</t>
   </si>
   <si>
-    <t>Q1</t>
+    <t>Q3</t>
   </si>
   <si>
     <t>Control</t>
   </si>
   <si>
-    <t>Q3</t>
-  </si>
-  <si>
     <t>Min</t>
   </si>
   <si>
+    <t>IUD</t>
+  </si>
+  <si>
     <t>Max</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>Moderate pain %</t>
   </si>
   <si>
+    <t>Mody et al, 2012</t>
+  </si>
+  <si>
     <t>Severe pain %</t>
   </si>
   <si>
@@ -92,15 +98,9 @@
     <t>0-100</t>
   </si>
   <si>
-    <t>IUD</t>
-  </si>
-  <si>
     <t>Speculum insertion</t>
   </si>
   <si>
-    <t>Mody et al, 2012</t>
-  </si>
-  <si>
     <t>https://www.sciencedirect.com/science/article/abs/pii/S0010782412004180?via%3Dihub</t>
   </si>
   <si>
@@ -113,6 +113,9 @@
     <t>IUD insertion</t>
   </si>
   <si>
+    <t>Afterwards</t>
+  </si>
+  <si>
     <t>Any</t>
   </si>
   <si>
@@ -131,24 +134,21 @@
     <t>https://www.ijrcog.org/index.php/ijrcog/article/view/91/91</t>
   </si>
   <si>
-    <t>Afterwards</t>
-  </si>
-  <si>
     <t>Cirik 2013</t>
   </si>
   <si>
     <t>0-10</t>
   </si>
   <si>
+    <t>Placebo</t>
+  </si>
+  <si>
     <t>Any (mostly parous)</t>
   </si>
   <si>
     <t>10 mL 1% lidocaine paracervically injected</t>
   </si>
   <si>
-    <t>Placebo</t>
-  </si>
-  <si>
     <t>10 mm 0.9% NaCl solution paracervically injected</t>
   </si>
   <si>
@@ -161,103 +161,103 @@
     <t>https://obgyn.onlinelibrary.wiley.com/doi/10.1111/jog.13308</t>
   </si>
   <si>
+    <t>Parous</t>
+  </si>
+  <si>
+    <t>10 mL lidocaine (20 mg/mL) paracervical block, and 2 mL at tenaculum site</t>
+  </si>
+  <si>
+    <t>No medication</t>
+  </si>
+  <si>
+    <t>Akers et al, 2017</t>
+  </si>
+  <si>
     <t>Karasu 2017</t>
   </si>
   <si>
-    <t>Parous</t>
-  </si>
-  <si>
-    <t>10 mL lidocaine (20 mg/mL) paracervical block, and 2 mL at tenaculum site</t>
-  </si>
-  <si>
-    <t>No medication</t>
-  </si>
-  <si>
-    <t>Akers et al, 2017</t>
-  </si>
-  <si>
     <t>https://journals.lww.com/greenjournal/abstract/2017/10000/reducing_pain_during_intrauterine_device.19.aspx</t>
   </si>
   <si>
+    <t>Nulliparous</t>
+  </si>
+  <si>
+    <t>1 mL of 1% lidocaine at the tenaculum site and 9 mL paracervical block</t>
+  </si>
+  <si>
+    <t>Sham block</t>
+  </si>
+  <si>
+    <t>Skyla IUD (13.5-mg levonorgestrel IUD)</t>
+  </si>
+  <si>
+    <t>Dogan et al, 2017</t>
+  </si>
+  <si>
+    <t>https://jcdr.net/article_fulltext.asp?issn=0973-709x&amp;year=2017&amp;volume=11&amp;issue=11&amp;page=QC09&amp;issn=0973-709x&amp;id=10854</t>
+  </si>
+  <si>
     <t>Akers 2017</t>
   </si>
   <si>
-    <t>Nulliparous</t>
-  </si>
-  <si>
-    <t>1 mL of 1% lidocaine at the tenaculum site and 9 mL paracervical block</t>
-  </si>
-  <si>
-    <t>Sham block</t>
-  </si>
-  <si>
-    <t>Skyla IUD (13.5-mg levonorgestrel IUD)</t>
-  </si>
-  <si>
-    <t>Dogan et al, 2017</t>
-  </si>
-  <si>
-    <t>https://jcdr.net/article_fulltext.asp?issn=0973-709x&amp;year=2017&amp;volume=11&amp;issue=11&amp;page=QC09&amp;issn=0973-709x&amp;id=10854</t>
+    <t>10 mL 2% lidocaine paracervically injected</t>
+  </si>
+  <si>
+    <t>No analgesic</t>
+  </si>
+  <si>
+    <t>CuT380A IUD (ParaGard)</t>
+  </si>
+  <si>
+    <t>Berens et al, 2017</t>
+  </si>
+  <si>
+    <t>https://clinicaltrials.gov/study/NCT02904915?term=(%22paracervical%20block%22%20OR%20%22cervical%20block%22%20OR%20%22lidocaine%22%20OR%20%22local%20anesthesia%22%20OR%20%22local%20anesthetic%22)%20AND%20(%22intrauterine%20device%22%20OR%20%22intrauterine%20contraceptive%22%20OR%20%22intrauterine%20contraception%22%20OR%20%22IUD%22%20OR%20%22IUC%22)&amp;rank=35</t>
   </si>
   <si>
     <t>Uterine sounding</t>
   </si>
   <si>
-    <t>10 mL 2% lidocaine paracervically injected</t>
-  </si>
-  <si>
-    <t>No analgesic</t>
-  </si>
-  <si>
-    <t>CuT380A IUD (ParaGard)</t>
-  </si>
-  <si>
-    <t>Berens et al, 2017</t>
-  </si>
-  <si>
-    <t>https://clinicaltrials.gov/study/NCT02904915?term=(%22paracervical%20block%22%20OR%20%22cervical%20block%22%20OR%20%22lidocaine%22%20OR%20%22local%20anesthesia%22%20OR%20%22local%20anesthetic%22)%20AND%20(%22intrauterine%20device%22%20OR%20%22intrauterine%20contraceptive%22%20OR%20%22intrauterine%20contraception%22%20OR%20%22IUD%22%20OR%20%22IUC%22)&amp;rank=35</t>
+    <t>2 cc 1% lidocaine at tenaculum site, 6 cc paracervical block</t>
+  </si>
+  <si>
+    <t>No local analgesia</t>
+  </si>
+  <si>
+    <t>Unspecified</t>
+  </si>
+  <si>
+    <t>Mody et al, 2018</t>
+  </si>
+  <si>
+    <t>https://journals.lww.com/greenjournal/abstract/2018/09000/paracervical_block_for_intrauterine_device.6.aspx</t>
+  </si>
+  <si>
+    <t>2 mL at tenaculum site and 18 mL paracervical block of 20 mL mixture: 18 mL of 1% lidocaine buffered with 2 mL 8.4% sodium bicarbonate</t>
+  </si>
+  <si>
+    <t>2 mL buffered lidocaine at tenaculum site and sham block</t>
+  </si>
+  <si>
+    <t>Mostly the larger framed levonorgestrel 52-mg and CuT380A IUDs</t>
+  </si>
+  <si>
+    <t>Khedr et al, 2024</t>
+  </si>
+  <si>
+    <t>https://journals.ekb.eg/article_343457_dd05f8e77ddd21a9540c9ce90802502f.pdf</t>
   </si>
   <si>
     <t>Dogan 2017</t>
   </si>
   <si>
+    <t>Copper T380A</t>
+  </si>
+  <si>
     <t>Berens 2017</t>
   </si>
   <si>
-    <t>2 cc 1% lidocaine at tenaculum site, 6 cc paracervical block</t>
-  </si>
-  <si>
-    <t>No local analgesia</t>
-  </si>
-  <si>
-    <t>Unspecified</t>
-  </si>
-  <si>
-    <t>Mody et al, 2018</t>
-  </si>
-  <si>
-    <t>https://journals.lww.com/greenjournal/abstract/2018/09000/paracervical_block_for_intrauterine_device.6.aspx</t>
-  </si>
-  <si>
-    <t>2 mL at tenaculum site and 18 mL paracervical block of 20 mL mixture: 18 mL of 1% lidocaine buffered with 2 mL 8.4% sodium bicarbonate</t>
-  </si>
-  <si>
-    <t>2 mL buffered lidocaine at tenaculum site and sham block</t>
-  </si>
-  <si>
-    <t>Mostly the larger framed levonorgestrel 52-mg and CuT380A IUDs</t>
-  </si>
-  <si>
-    <t>Khedr et al, 2024</t>
-  </si>
-  <si>
     <t>Mody 2018</t>
-  </si>
-  <si>
-    <t>https://journals.ekb.eg/article_343457_dd05f8e77ddd21a9540c9ce90802502f.pdf</t>
-  </si>
-  <si>
-    <t>Copper T380A</t>
   </si>
   <si>
     <t>Overall</t>
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -564,21 +564,21 @@
         <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>29</v>
@@ -593,27 +593,27 @@
         <v>24.0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4">
         <v>64.0</v>
@@ -625,10 +625,10 @@
         <v>30.0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>45</v>
@@ -657,13 +657,13 @@
         <v>49.0</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>46</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>54</v>
@@ -689,27 +689,27 @@
         <v>48.0</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C6" s="4">
         <v>88.0</v>
@@ -721,16 +721,16 @@
         <v>46.0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>41</v>
@@ -738,10 +738,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C7" s="4">
         <v>50.0</v>
@@ -753,16 +753,16 @@
         <v>25.0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4">
         <v>64.0</v>
@@ -785,27 +785,27 @@
         <v>31.0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4">
         <v>138.0</v>
@@ -817,19 +817,19 @@
         <v>68.0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -883,42 +883,42 @@
         <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4">
         <v>13.8</v>
@@ -950,13 +950,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>30</v>
@@ -991,16 +991,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4">
         <v>44.7</v>
@@ -1032,16 +1032,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4">
         <v>18.8</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>31</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4">
         <v>37.3</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1196,16 +1196,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="4">
         <v>20.5</v>
@@ -1237,13 +1237,13 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
@@ -1287,7 +1287,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1320,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1353,7 +1353,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1386,7 +1386,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1416,10 +1416,10 @@
         <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1449,10 +1449,10 @@
         <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1476,16 +1476,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="4">
         <v>3.9</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>30</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>41</v>
@@ -1563,7 +1563,7 @@
         <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="4">
         <v>2.65</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>41</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>41</v>
@@ -1641,7 +1641,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="4">
         <v>2.925</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>41</v>
@@ -1710,16 +1710,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1739,16 +1739,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1768,16 +1768,16 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1797,16 +1797,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1826,16 +1826,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1859,16 +1859,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -1892,16 +1892,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -1925,16 +1925,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -1958,16 +1958,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -2024,16 +2024,16 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2057,16 +2057,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>41</v>
@@ -2099,7 +2099,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="4">
         <v>3.69</v>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>41</v>
@@ -2160,16 +2160,16 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" s="4">
         <v>3.02</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>30</v>
@@ -2230,16 +2230,16 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="4">
         <v>2.4</v>
@@ -2261,13 +2261,13 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>30</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>41</v>
@@ -2301,7 +2301,7 @@
         <v>31</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" s="4">
         <v>2.1</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>41</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>41</v>
@@ -2363,7 +2363,7 @@
         <v>32</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" s="4">
         <v>2.6</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>41</v>
@@ -2416,16 +2416,16 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2449,16 +2449,16 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -2482,16 +2482,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -2515,16 +2515,16 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2548,16 +2548,16 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2581,16 +2581,16 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2647,16 +2647,16 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2680,16 +2680,16 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -2746,16 +2746,16 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -2779,16 +2779,16 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -2812,16 +2812,16 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -2848,13 +2848,13 @@
         <v>83</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58" s="4">
         <v>51.0</v>
@@ -2879,13 +2879,13 @@
         <v>83</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E59" s="4">
         <v>53.4</v>
@@ -2910,13 +2910,13 @@
         <v>83</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60" s="4">
         <v>18.4</v>
@@ -2941,13 +2941,13 @@
         <v>83</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E61" s="4">
         <v>10.9</v>
@@ -2972,13 +2972,13 @@
         <v>83</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E62" s="4">
         <v>28.9</v>
@@ -3003,13 +3003,13 @@
         <v>83</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E63" s="4">
         <v>58.4</v>
@@ -3034,13 +3034,13 @@
         <v>83</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E64" s="4">
         <v>28.0</v>
@@ -3065,13 +3065,13 @@
         <v>83</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E65" s="4">
         <v>47.8</v>
@@ -3096,13 +3096,13 @@
         <v>83</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E66" s="4">
         <v>20.9</v>
@@ -3127,13 +3127,13 @@
         <v>83</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E67" s="4">
         <v>37.4</v>
@@ -3158,13 +3158,13 @@
         <v>83</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E68" s="4">
         <v>5.9</v>
@@ -3189,13 +3189,13 @@
         <v>83</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E69" s="4">
         <v>16.9</v>
